--- a/2차/망최적화/100_station_list.xlsx
+++ b/2차/망최적화/100_station_list.xlsx
@@ -14,561 +14,576 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="198" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="203" uniqueCount="201">
   <si>
     <t>code</t>
   </si>
   <si>
+    <t>CHSG</t>
+  </si>
+  <si>
+    <t>CHUL</t>
+  </si>
+  <si>
+    <t>CHWN</t>
+  </si>
+  <si>
+    <t>CJDO</t>
+  </si>
+  <si>
+    <t>DAMY</t>
+  </si>
+  <si>
+    <t>DOND</t>
+  </si>
+  <si>
+    <t>DONH</t>
+  </si>
+  <si>
+    <t>GANH</t>
+  </si>
+  <si>
+    <t>GGEO</t>
+  </si>
+  <si>
+    <t>GMDO</t>
+  </si>
+  <si>
+    <t>GOJE</t>
+  </si>
+  <si>
+    <t>GYJU</t>
+  </si>
+  <si>
+    <t>HADG</t>
+  </si>
+  <si>
+    <t>HCHN</t>
+  </si>
+  <si>
+    <t>HONC</t>
+  </si>
+  <si>
+    <t>HSDO</t>
+  </si>
+  <si>
+    <t>ICHN</t>
+  </si>
+  <si>
+    <t>IMJA</t>
+  </si>
+  <si>
+    <t>JAHG</t>
+  </si>
+  <si>
+    <t>JANS</t>
+  </si>
+  <si>
+    <t>JIND</t>
+  </si>
+  <si>
+    <t>JJHG</t>
+  </si>
+  <si>
+    <t>KUSN</t>
+  </si>
+  <si>
+    <t>NAMH</t>
+  </si>
+  <si>
+    <t>NAMY</t>
+  </si>
+  <si>
+    <t>POHN</t>
+  </si>
+  <si>
+    <t>PSJA</t>
+  </si>
+  <si>
+    <t>PUSN</t>
+  </si>
+  <si>
+    <t>SEJN</t>
+  </si>
+  <si>
+    <t>SEOS</t>
+  </si>
+  <si>
+    <t>SGWI</t>
+  </si>
+  <si>
+    <t>SMAN</t>
+  </si>
+  <si>
+    <t>SNJU</t>
+  </si>
+  <si>
+    <t>SSAN</t>
+  </si>
+  <si>
+    <t>SUNJ</t>
+  </si>
+  <si>
+    <t>SWGS</t>
+  </si>
+  <si>
+    <t>ULDO</t>
+  </si>
+  <si>
+    <t>WOLS</t>
+  </si>
+  <si>
+    <t>WULJ</t>
+  </si>
+  <si>
+    <t>YNGU</t>
+  </si>
+  <si>
+    <t>YODK</t>
+  </si>
+  <si>
+    <t>YOWL</t>
+  </si>
+  <si>
+    <t>YYAN</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>청송</t>
+  </si>
+  <si>
+    <t>철원</t>
+  </si>
+  <si>
+    <t>창원</t>
+  </si>
+  <si>
+    <t>담양</t>
+  </si>
+  <si>
+    <t>동두천</t>
+  </si>
+  <si>
+    <t>동해</t>
+  </si>
+  <si>
+    <t>강화</t>
+  </si>
+  <si>
+    <t>가거도</t>
+  </si>
+  <si>
+    <t>거제도</t>
+  </si>
+  <si>
+    <t>경주</t>
+  </si>
+  <si>
+    <t>하동</t>
+  </si>
+  <si>
+    <t>화천</t>
+  </si>
+  <si>
+    <t>홍천</t>
+  </si>
+  <si>
+    <t>이천</t>
+  </si>
+  <si>
+    <t>임자</t>
+  </si>
+  <si>
+    <t>장흥</t>
+  </si>
+  <si>
+    <t>장수</t>
+  </si>
+  <si>
+    <t>진도</t>
+  </si>
+  <si>
+    <t>제주한경</t>
+  </si>
+  <si>
+    <t>군산</t>
+  </si>
+  <si>
+    <t>남해</t>
+  </si>
+  <si>
+    <t>남양주</t>
+  </si>
+  <si>
+    <t>포항</t>
+  </si>
+  <si>
+    <t>부산장안</t>
+  </si>
+  <si>
+    <t>부산</t>
+  </si>
+  <si>
+    <t>세종</t>
+  </si>
+  <si>
+    <t>서산</t>
+  </si>
+  <si>
+    <t>서귀포</t>
+  </si>
+  <si>
+    <t>새만금</t>
+  </si>
+  <si>
+    <t>상주</t>
+  </si>
+  <si>
+    <t>성산</t>
+  </si>
+  <si>
+    <t>성주</t>
+  </si>
+  <si>
+    <t>수원고색</t>
+  </si>
+  <si>
+    <t>울산</t>
+  </si>
+  <si>
+    <t>울진</t>
+  </si>
+  <si>
+    <t>양구</t>
+  </si>
+  <si>
+    <t>영덕</t>
+  </si>
+  <si>
+    <t>영월</t>
+  </si>
+  <si>
+    <t>양양</t>
+  </si>
+  <si>
+    <t>ANSG</t>
+  </si>
+  <si>
+    <t>BOEN</t>
+  </si>
+  <si>
+    <t>BONH</t>
+  </si>
+  <si>
+    <t>BSNG</t>
+  </si>
+  <si>
+    <t>CCSB</t>
+  </si>
+  <si>
+    <t>CHEN</t>
+  </si>
+  <si>
     <t>CHJU</t>
   </si>
   <si>
-    <t>CHSG</t>
-  </si>
-  <si>
-    <t>CHUL</t>
-  </si>
-  <si>
-    <t>CHWN</t>
-  </si>
-  <si>
-    <t>DAMY</t>
-  </si>
-  <si>
-    <t>DONH</t>
-  </si>
-  <si>
-    <t>GANH</t>
-  </si>
-  <si>
-    <t>GGEO</t>
+    <t>CHLW</t>
+  </si>
+  <si>
+    <t>CHNG</t>
+  </si>
+  <si>
+    <t>CHYG</t>
+  </si>
+  <si>
+    <t>CNJU</t>
+  </si>
+  <si>
+    <t>DANJ</t>
+  </si>
+  <si>
+    <t>GHDG</t>
+  </si>
+  <si>
+    <t>GNGJ</t>
+  </si>
+  <si>
+    <t>GOCH</t>
   </si>
   <si>
     <t>GOHG</t>
   </si>
   <si>
-    <t>GOJE</t>
-  </si>
-  <si>
-    <t>GYJU</t>
-  </si>
-  <si>
-    <t>HADG</t>
-  </si>
-  <si>
-    <t>HCHN</t>
-  </si>
-  <si>
-    <t>HONC</t>
-  </si>
-  <si>
-    <t>ICHN</t>
-  </si>
-  <si>
-    <t>IMJA</t>
-  </si>
-  <si>
-    <t>JAHG</t>
-  </si>
-  <si>
-    <t>JANS</t>
-  </si>
-  <si>
-    <t>JIND</t>
-  </si>
-  <si>
-    <t>JJHG</t>
-  </si>
-  <si>
-    <t>KUSN</t>
-  </si>
-  <si>
-    <t>NAMH</t>
+    <t>GOSG</t>
+  </si>
+  <si>
+    <t>GSAN</t>
+  </si>
+  <si>
+    <t>GYOI</t>
+  </si>
+  <si>
+    <t>HCSN</t>
+  </si>
+  <si>
+    <t>ICOR</t>
+  </si>
+  <si>
+    <t>INCH</t>
+  </si>
+  <si>
+    <t>INJE</t>
+  </si>
+  <si>
+    <t>JECH</t>
+  </si>
+  <si>
+    <t>JJNG</t>
+  </si>
+  <si>
+    <t>JSUN</t>
+  </si>
+  <si>
+    <t>JUNG</t>
+  </si>
+  <si>
+    <t>JUNJ</t>
+  </si>
+  <si>
+    <t>KIMC</t>
+  </si>
+  <si>
+    <t>KUNW</t>
+  </si>
+  <si>
+    <t>KWNJ</t>
+  </si>
+  <si>
+    <t>MUAN</t>
+  </si>
+  <si>
+    <t>MUJU</t>
+  </si>
+  <si>
+    <t>MYSO</t>
+  </si>
+  <si>
+    <t>NAMW</t>
+  </si>
+  <si>
+    <t>NSAN</t>
   </si>
   <si>
     <t>OJBU</t>
   </si>
   <si>
-    <t>SEJN</t>
-  </si>
-  <si>
-    <t>SEOS</t>
-  </si>
-  <si>
-    <t>SGWI</t>
-  </si>
-  <si>
-    <t>SMAN</t>
-  </si>
-  <si>
-    <t>SNJU</t>
-  </si>
-  <si>
-    <t>SSAN</t>
-  </si>
-  <si>
-    <t>SUNJ</t>
-  </si>
-  <si>
-    <t>SWGS</t>
+    <t>PAJU</t>
+  </si>
+  <si>
+    <t>PCHN</t>
+  </si>
+  <si>
+    <t>PJMS</t>
+  </si>
+  <si>
+    <t>POCN</t>
+  </si>
+  <si>
+    <t>SIAN</t>
+  </si>
+  <si>
+    <t>SONC</t>
+  </si>
+  <si>
+    <t>SOUL</t>
+  </si>
+  <si>
+    <t>SUWN</t>
+  </si>
+  <si>
+    <t>TABK</t>
+  </si>
+  <si>
+    <t>TEGN</t>
   </si>
   <si>
     <t>WNDO</t>
   </si>
   <si>
-    <t>WOLS</t>
-  </si>
-  <si>
-    <t>WULJ</t>
-  </si>
-  <si>
-    <t>YNGU</t>
-  </si>
-  <si>
-    <t>YODK</t>
-  </si>
-  <si>
-    <t>YOWL</t>
-  </si>
-  <si>
-    <t>YYAN</t>
-  </si>
-  <si>
-    <t>name</t>
+    <t>WNJU</t>
+  </si>
+  <si>
+    <t>WSJG</t>
+  </si>
+  <si>
+    <t>WSSN</t>
+  </si>
+  <si>
+    <t>YANJ</t>
+  </si>
+  <si>
+    <t>YANP</t>
+  </si>
+  <si>
+    <t>YCHG</t>
+  </si>
+  <si>
+    <t>YCIG</t>
+  </si>
+  <si>
+    <t>YCMP</t>
+  </si>
+  <si>
+    <t>YDKG</t>
+  </si>
+  <si>
+    <t>YEOJ</t>
+  </si>
+  <si>
+    <t>YONK</t>
+  </si>
+  <si>
+    <t>안성</t>
+  </si>
+  <si>
+    <t>보은</t>
+  </si>
+  <si>
+    <t>봉화</t>
+  </si>
+  <si>
+    <t>보성</t>
+  </si>
+  <si>
+    <t>춘천신북</t>
+  </si>
+  <si>
+    <t>천안</t>
   </si>
   <si>
     <t>제주</t>
   </si>
   <si>
-    <t>청송</t>
-  </si>
-  <si>
-    <t>철원</t>
-  </si>
-  <si>
-    <t>창원</t>
-  </si>
-  <si>
-    <t>담양</t>
-  </si>
-  <si>
-    <t>동해</t>
-  </si>
-  <si>
-    <t>강화</t>
-  </si>
-  <si>
-    <t>가거도</t>
+    <t>철원(서면)</t>
+  </si>
+  <si>
+    <t>창녕</t>
+  </si>
+  <si>
+    <t>청양</t>
+  </si>
+  <si>
+    <t>청주</t>
+  </si>
+  <si>
+    <t>당진</t>
+  </si>
+  <si>
+    <t>김해대감</t>
+  </si>
+  <si>
+    <t>강릉구정</t>
+  </si>
+  <si>
+    <t>거창</t>
   </si>
   <si>
     <t>고흥</t>
   </si>
   <si>
-    <t>거제도</t>
-  </si>
-  <si>
-    <t>경주</t>
-  </si>
-  <si>
-    <t>하동</t>
-  </si>
-  <si>
-    <t>화천</t>
-  </si>
-  <si>
-    <t>홍천</t>
-  </si>
-  <si>
-    <t>이천</t>
-  </si>
-  <si>
-    <t>임자</t>
-  </si>
-  <si>
-    <t>장흥</t>
-  </si>
-  <si>
-    <t>장수</t>
-  </si>
-  <si>
-    <t>진도</t>
-  </si>
-  <si>
-    <t>제주한경</t>
-  </si>
-  <si>
-    <t>군산</t>
-  </si>
-  <si>
-    <t>남해</t>
+    <t>고성</t>
+  </si>
+  <si>
+    <t>괴산</t>
+  </si>
+  <si>
+    <t>경주외동</t>
+  </si>
+  <si>
+    <t>화천사내</t>
+  </si>
+  <si>
+    <t>인천옥련</t>
+  </si>
+  <si>
+    <t>인천</t>
+  </si>
+  <si>
+    <t>인제</t>
+  </si>
+  <si>
+    <t>제천</t>
+  </si>
+  <si>
+    <t>정선</t>
+  </si>
+  <si>
+    <t>정읍</t>
+  </si>
+  <si>
+    <t>전주</t>
+  </si>
+  <si>
+    <t>김천</t>
+  </si>
+  <si>
+    <t>군위</t>
+  </si>
+  <si>
+    <t>광주</t>
+  </si>
+  <si>
+    <t>무안</t>
+  </si>
+  <si>
+    <t>무주</t>
+  </si>
+  <si>
+    <t>밀양산외</t>
+  </si>
+  <si>
+    <t>남원</t>
+  </si>
+  <si>
+    <t>논산</t>
   </si>
   <si>
     <t>의정부</t>
   </si>
   <si>
-    <t>세종</t>
-  </si>
-  <si>
-    <t>서산</t>
-  </si>
-  <si>
-    <t>서귀포</t>
-  </si>
-  <si>
-    <t>새만금</t>
-  </si>
-  <si>
-    <t>상주</t>
-  </si>
-  <si>
-    <t>성산</t>
-  </si>
-  <si>
-    <t>성주</t>
-  </si>
-  <si>
-    <t>수원고색</t>
+    <t>파주</t>
+  </si>
+  <si>
+    <t>평창</t>
+  </si>
+  <si>
+    <t>파주문산</t>
+  </si>
+  <si>
+    <t>포천</t>
+  </si>
+  <si>
+    <t>신안</t>
+  </si>
+  <si>
+    <t>순천</t>
+  </si>
+  <si>
+    <t>서울</t>
+  </si>
+  <si>
+    <t>수원</t>
+  </si>
+  <si>
+    <t>태백</t>
+  </si>
+  <si>
+    <t>대구</t>
   </si>
   <si>
     <t>완도</t>
-  </si>
-  <si>
-    <t>울산</t>
-  </si>
-  <si>
-    <t>울진</t>
-  </si>
-  <si>
-    <t>양구</t>
-  </si>
-  <si>
-    <t>영덕</t>
-  </si>
-  <si>
-    <t>영월</t>
-  </si>
-  <si>
-    <t>양양</t>
-  </si>
-  <si>
-    <t>ANSG</t>
-  </si>
-  <si>
-    <t>BOEN</t>
-  </si>
-  <si>
-    <t>BONH</t>
-  </si>
-  <si>
-    <t>BSNG</t>
-  </si>
-  <si>
-    <t>CCSB</t>
-  </si>
-  <si>
-    <t>CHEN</t>
-  </si>
-  <si>
-    <t>CHLW</t>
-  </si>
-  <si>
-    <t>CHNG</t>
-  </si>
-  <si>
-    <t>CHYG</t>
-  </si>
-  <si>
-    <t>CNJU</t>
-  </si>
-  <si>
-    <t>DANJ</t>
-  </si>
-  <si>
-    <t>DOND</t>
-  </si>
-  <si>
-    <t>GHDG</t>
-  </si>
-  <si>
-    <t>GNGJ</t>
-  </si>
-  <si>
-    <t>GOCH</t>
-  </si>
-  <si>
-    <t>GOSG</t>
-  </si>
-  <si>
-    <t>GSAN</t>
-  </si>
-  <si>
-    <t>GYOI</t>
-  </si>
-  <si>
-    <t>HCSN</t>
-  </si>
-  <si>
-    <t>ICOR</t>
-  </si>
-  <si>
-    <t>INCH</t>
-  </si>
-  <si>
-    <t>INJE</t>
-  </si>
-  <si>
-    <t>JECH</t>
-  </si>
-  <si>
-    <t>JSUN</t>
-  </si>
-  <si>
-    <t>JUNG</t>
-  </si>
-  <si>
-    <t>JUNJ</t>
-  </si>
-  <si>
-    <t>KIMC</t>
-  </si>
-  <si>
-    <t>KUNW</t>
-  </si>
-  <si>
-    <t>KWNJ</t>
-  </si>
-  <si>
-    <t>MUAN</t>
-  </si>
-  <si>
-    <t>MUJU</t>
-  </si>
-  <si>
-    <t>MYSO</t>
-  </si>
-  <si>
-    <t>NAMW</t>
-  </si>
-  <si>
-    <t>NAMY</t>
-  </si>
-  <si>
-    <t>NSAN</t>
-  </si>
-  <si>
-    <t>PAJU</t>
-  </si>
-  <si>
-    <t>PCHN</t>
-  </si>
-  <si>
-    <t>PJMS</t>
-  </si>
-  <si>
-    <t>POCN</t>
-  </si>
-  <si>
-    <t>POHN</t>
-  </si>
-  <si>
-    <t>PSJA</t>
-  </si>
-  <si>
-    <t>PUSN</t>
-  </si>
-  <si>
-    <t>SIAN</t>
-  </si>
-  <si>
-    <t>SONC</t>
-  </si>
-  <si>
-    <t>SOUL</t>
-  </si>
-  <si>
-    <t>SUWN</t>
-  </si>
-  <si>
-    <t>TABK</t>
-  </si>
-  <si>
-    <t>TEGN</t>
-  </si>
-  <si>
-    <t>WNJU</t>
-  </si>
-  <si>
-    <t>WSJG</t>
-  </si>
-  <si>
-    <t>WSSN</t>
-  </si>
-  <si>
-    <t>YANJ</t>
-  </si>
-  <si>
-    <t>YANP</t>
-  </si>
-  <si>
-    <t>YCHG</t>
-  </si>
-  <si>
-    <t>YCIG</t>
-  </si>
-  <si>
-    <t>YCMP</t>
-  </si>
-  <si>
-    <t>YDKG</t>
-  </si>
-  <si>
-    <t>YEOJ</t>
-  </si>
-  <si>
-    <t>YONK</t>
-  </si>
-  <si>
-    <t>안성</t>
-  </si>
-  <si>
-    <t>보은</t>
-  </si>
-  <si>
-    <t>봉화</t>
-  </si>
-  <si>
-    <t>보성</t>
-  </si>
-  <si>
-    <t>춘천신북</t>
-  </si>
-  <si>
-    <t>천안</t>
-  </si>
-  <si>
-    <t>철원(서면)</t>
-  </si>
-  <si>
-    <t>창녕</t>
-  </si>
-  <si>
-    <t>청양</t>
-  </si>
-  <si>
-    <t>청주</t>
-  </si>
-  <si>
-    <t>당진</t>
-  </si>
-  <si>
-    <t>동두천</t>
-  </si>
-  <si>
-    <t>김해대감</t>
-  </si>
-  <si>
-    <t>강릉구정</t>
-  </si>
-  <si>
-    <t>거창</t>
-  </si>
-  <si>
-    <t>고성</t>
-  </si>
-  <si>
-    <t>괴산</t>
-  </si>
-  <si>
-    <t>경주외동</t>
-  </si>
-  <si>
-    <t>화천사내</t>
-  </si>
-  <si>
-    <t>인천옥련</t>
-  </si>
-  <si>
-    <t>인천</t>
-  </si>
-  <si>
-    <t>인제</t>
-  </si>
-  <si>
-    <t>제천</t>
-  </si>
-  <si>
-    <t>정선</t>
-  </si>
-  <si>
-    <t>정읍</t>
-  </si>
-  <si>
-    <t>전주</t>
-  </si>
-  <si>
-    <t>김천</t>
-  </si>
-  <si>
-    <t>군위</t>
-  </si>
-  <si>
-    <t>광주</t>
-  </si>
-  <si>
-    <t>무안</t>
-  </si>
-  <si>
-    <t>무주</t>
-  </si>
-  <si>
-    <t>밀양산외</t>
-  </si>
-  <si>
-    <t>남원</t>
-  </si>
-  <si>
-    <t>남양주</t>
-  </si>
-  <si>
-    <t>논산</t>
-  </si>
-  <si>
-    <t>파주</t>
-  </si>
-  <si>
-    <t>평창</t>
-  </si>
-  <si>
-    <t>파주문산</t>
-  </si>
-  <si>
-    <t>포천</t>
-  </si>
-  <si>
-    <t>포항</t>
-  </si>
-  <si>
-    <t>부산장안</t>
-  </si>
-  <si>
-    <t>부산</t>
-  </si>
-  <si>
-    <t>신안</t>
-  </si>
-  <si>
-    <t>순천</t>
-  </si>
-  <si>
-    <t>서울</t>
-  </si>
-  <si>
-    <t>수원</t>
-  </si>
-  <si>
-    <t>태백</t>
-  </si>
-  <si>
-    <t>대구</t>
   </si>
   <si>
     <t>원주</t>
@@ -647,10 +662,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="true"/>
+    <col min="1" max="1" width="6.85546875" customWidth="true"/>
     <col min="2" max="2" width="7.42578125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -659,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -667,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +690,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -683,23 +698,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>43</v>
-      </c>
+      <c r="B5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -707,7 +720,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +728,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -723,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -731,23 +744,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>49</v>
-      </c>
+      <c r="B11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +766,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +774,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +782,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -779,23 +790,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>55</v>
-      </c>
+      <c r="B17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +812,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -811,7 +820,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -819,7 +828,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -827,7 +836,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -835,7 +844,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -843,7 +852,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -851,7 +860,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -859,7 +868,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -867,7 +876,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
@@ -875,7 +884,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +892,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -891,7 +900,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -899,7 +908,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
@@ -907,7 +916,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -915,7 +924,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
@@ -923,7 +932,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
@@ -931,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36">
@@ -939,7 +948,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
@@ -947,23 +956,61 @@
         <v>36</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>76</v>
-      </c>
+      <c r="B38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -984,479 +1031,477 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>161</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
